--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2760-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2760-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0879BA04-EB73-4BE0-AF1E-4088807EC0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{786CE562-2157-40BB-BD58-5775F0F75FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{E2F64A13-8BE8-41BD-A558-D472A92D798B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{FA7C1AD1-6A95-441A-B940-351AD23D3285}"/>
   </bookViews>
   <sheets>
     <sheet name="2760-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1457,22 +1457,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3BB4F56-7A21-4A33-A55E-F4843F54A58D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50F05FF8-A3DE-4A44-B572-DCDEC3A0216C}">
   <dimension ref="A1:R17"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="3" width="8" customWidth="1"/>
-    <col min="4" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="3" width="10" customWidth="1"/>
+    <col min="4" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1500,7 +1500,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1530,7 +1530,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1626,7 +1626,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1680,7 +1680,7 @@
         <v>2.77</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>2.77</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>5.03</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>5.03</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>6.66</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>6.66</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2022</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
         <v>38</v>
       </c>
